--- a/Result/10-25-25/S&P500stock_10-25-25period252RS90.xlsx
+++ b/Result/10-25-25/S&P500stock_10-25-25period252RS90.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding Project/StockAnalysis/Result/10-25-25/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22354CB3-CC17-DE40-8A2C-0EB8B03E9008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -358,12 +364,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -371,8 +377,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -418,17 +431,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -466,7 +487,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -500,6 +521,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -534,9 +556,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -709,9 +732,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:42">
       <c r="A1" s="1" t="s">
@@ -846,10 +869,10 @@
         <v>42</v>
       </c>
       <c r="B2">
-        <v>95.82504970178927</v>
+        <v>95.825049701789268</v>
       </c>
       <c r="C2">
-        <v>99.80119284294234</v>
+        <v>99.801192842942342</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -861,7 +884,7 @@
         <v>38.28</v>
       </c>
       <c r="G2">
-        <v>0.4915684793087775</v>
+        <v>0.49156847930877751</v>
       </c>
       <c r="H2">
         <v>1.554850923555122</v>
@@ -870,7 +893,7 @@
         <v>2.99</v>
       </c>
       <c r="J2">
-        <v>0.2940180693765561</v>
+        <v>0.29401806937655611</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -882,16 +905,16 @@
         <v>37.91599884033203</v>
       </c>
       <c r="N2">
-        <v>36.8444995880127</v>
+        <v>36.844499588012702</v>
       </c>
       <c r="O2">
-        <v>30.37759986877441</v>
+        <v>30.377599868774411</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>23.68194993019104</v>
+        <v>23.681949930191038</v>
       </c>
       <c r="R2">
         <v>1.03</v>
@@ -912,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>17.67</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="Z2">
         <v>41.12</v>
@@ -921,7 +944,7 @@
         <v>182.11</v>
       </c>
       <c r="AB2">
-        <v>-2.26</v>
+        <v>-2.2599999999999998</v>
       </c>
       <c r="AC2">
         <v>346.06</v>
@@ -936,7 +959,7 @@
         <v>-252.63</v>
       </c>
       <c r="AG2">
-        <v>-533.33</v>
+        <v>-533.33000000000004</v>
       </c>
       <c r="AH2">
         <v>99.23</v>
@@ -963,7 +986,7 @@
         <v>3133.33</v>
       </c>
       <c r="AP2">
-        <v>81.55287955371639</v>
+        <v>81.552879553716394</v>
       </c>
     </row>
     <row r="3" spans="1:42">
@@ -971,7 +994,7 @@
         <v>43</v>
       </c>
       <c r="B3">
-        <v>98.21073558648111</v>
+        <v>98.210735586481107</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -986,37 +1009,37 @@
         <v>219.02</v>
       </c>
       <c r="G3">
-        <v>0.7450802129514748</v>
+        <v>0.74508021295147475</v>
       </c>
       <c r="H3">
-        <v>2.189590047299282</v>
+        <v>2.1895900472992822</v>
       </c>
       <c r="I3">
         <v>3.81</v>
       </c>
       <c r="J3">
-        <v>0.9337023959798953</v>
+        <v>0.93370239597989535</v>
       </c>
       <c r="K3">
         <v>3.27</v>
       </c>
       <c r="L3">
-        <v>0.7176125170849381</v>
+        <v>0.71761251708493812</v>
       </c>
       <c r="M3">
-        <v>206.652001953125</v>
+        <v>206.65200195312499</v>
       </c>
       <c r="N3">
-        <v>192.1005012512207</v>
+        <v>192.10050125122069</v>
       </c>
       <c r="O3">
-        <v>159.4632014465332</v>
+        <v>159.46320144653319</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>114.3774502944946</v>
+        <v>114.37745029449459</v>
       </c>
       <c r="R3">
         <v>1.08</v>
@@ -1025,7 +1048,7 @@
         <v>1.2</v>
       </c>
       <c r="U3">
-        <v>24.44444444444444</v>
+        <v>24.444444444444439</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -1058,7 +1081,7 @@
         <v>17.2</v>
       </c>
       <c r="AF3">
-        <v>19.01</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AG3">
         <v>-15.48</v>
@@ -1088,7 +1111,7 @@
         <v>69.34</v>
       </c>
       <c r="AP3">
-        <v>80.57399316042208</v>
+        <v>80.573993160422077</v>
       </c>
     </row>
     <row r="4" spans="1:42">
@@ -1096,10 +1119,10 @@
         <v>44</v>
       </c>
       <c r="B4">
-        <v>99.60238568588468</v>
+        <v>99.602385685884684</v>
       </c>
       <c r="C4">
-        <v>99.00596421471172</v>
+        <v>99.005964214711724</v>
       </c>
       <c r="D4">
         <v>150</v>
@@ -1111,7 +1134,7 @@
         <v>620</v>
       </c>
       <c r="G4">
-        <v>2.528918638706959</v>
+        <v>2.5289186387069589</v>
       </c>
       <c r="H4">
         <v>2.336836875061806</v>
@@ -1120,37 +1143,37 @@
         <v>4.92</v>
       </c>
       <c r="J4">
-        <v>1.799616545406367</v>
+        <v>1.7996165454063671</v>
       </c>
       <c r="K4">
-        <v>4.11</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="L4">
-        <v>1.477988372508562</v>
+        <v>1.4779883725085621</v>
       </c>
       <c r="M4">
         <v>578.6200073242187</v>
       </c>
       <c r="N4">
-        <v>620.0340026855469</v>
+        <v>620.03400268554685</v>
       </c>
       <c r="O4">
-        <v>568.2923992919922</v>
+        <v>568.29239929199218</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>399.4146257781982</v>
+        <v>399.41462577819817</v>
       </c>
       <c r="R4">
         <v>0.93</v>
       </c>
       <c r="S4">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="U4">
-        <v>18.33333333333333</v>
+        <v>18.333333333333329</v>
       </c>
       <c r="V4" t="b">
         <v>0</v>
@@ -1210,7 +1233,7 @@
         <v>5.16</v>
       </c>
       <c r="AO4">
-        <v>-32.37</v>
+        <v>-32.369999999999997</v>
       </c>
       <c r="AP4">
         <v>73.01627321585238</v>
@@ -1239,40 +1262,40 @@
         <v>1.601937780836276</v>
       </c>
       <c r="H5">
-        <v>1.791242330433989</v>
+        <v>1.7912423304339891</v>
       </c>
       <c r="I5">
         <v>3.36</v>
       </c>
       <c r="J5">
-        <v>0.5826561191853797</v>
+        <v>0.58265611918537974</v>
       </c>
       <c r="K5">
         <v>5.28</v>
       </c>
       <c r="L5">
-        <v>2.537083313991465</v>
+        <v>2.5370833139914648</v>
       </c>
       <c r="M5">
-        <v>20.31599998474121</v>
+        <v>20.315999984741211</v>
       </c>
       <c r="N5">
         <v>18.92900018692017</v>
       </c>
       <c r="O5">
-        <v>16.4060001373291</v>
+        <v>16.406000137329102</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>11.87660002946854</v>
+        <v>11.876600029468539</v>
       </c>
       <c r="R5">
         <v>1.07</v>
       </c>
       <c r="S5">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -1305,7 +1328,7 @@
         <v>115.52</v>
       </c>
       <c r="AE5">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="AF5">
         <v>455.56</v>
@@ -1338,7 +1361,7 @@
         <v>-141.94</v>
       </c>
       <c r="AP5">
-        <v>64.88284391557642</v>
+        <v>64.882843915576416</v>
       </c>
     </row>
     <row r="6" spans="1:42">
@@ -1346,10 +1369,10 @@
         <v>46</v>
       </c>
       <c r="B6">
-        <v>97.4155069582505</v>
+        <v>97.415506958250504</v>
       </c>
       <c r="C6">
-        <v>90.65606361829026</v>
+        <v>90.656063618290261</v>
       </c>
       <c r="D6">
         <v>35</v>
@@ -1361,7 +1384,7 @@
         <v>354.13</v>
       </c>
       <c r="G6">
-        <v>0.7452938023673698</v>
+        <v>0.74529380236736975</v>
       </c>
       <c r="H6">
         <v>1.877595098052123</v>
@@ -1370,28 +1393,28 @@
         <v>3.07</v>
       </c>
       <c r="J6">
-        <v>0.3564262963622475</v>
+        <v>0.35642629636224749</v>
       </c>
       <c r="K6">
         <v>2.87</v>
       </c>
       <c r="L6">
-        <v>0.3555287764070224</v>
+        <v>0.35552877640702241</v>
       </c>
       <c r="M6">
-        <v>346.1239990234375</v>
+        <v>346.12399902343748</v>
       </c>
       <c r="N6">
-        <v>342.0529983520508</v>
+        <v>342.05299835205079</v>
       </c>
       <c r="O6">
-        <v>331.652001953125</v>
+        <v>331.65200195312502</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>255.2484999084473</v>
+        <v>255.24849990844729</v>
       </c>
       <c r="R6">
         <v>1.01</v>
@@ -1424,16 +1447,16 @@
         <v>13.91</v>
       </c>
       <c r="AC6">
-        <v>38.63</v>
+        <v>38.630000000000003</v>
       </c>
       <c r="AD6">
-        <v>311.84</v>
+        <v>311.83999999999997</v>
       </c>
       <c r="AE6">
         <v>27.08</v>
       </c>
       <c r="AF6">
-        <v>-16.19</v>
+        <v>-16.190000000000001</v>
       </c>
       <c r="AG6">
         <v>-10.26</v>
@@ -1463,7 +1486,7 @@
         <v>54.25</v>
       </c>
       <c r="AP6">
-        <v>59.99381280778724</v>
+        <v>59.993812807787243</v>
       </c>
     </row>
     <row r="7" spans="1:42">
@@ -1471,10 +1494,10 @@
         <v>47</v>
       </c>
       <c r="B7">
-        <v>96.81908548707754</v>
+        <v>96.819085487077544</v>
       </c>
       <c r="C7">
-        <v>97.61431411530815</v>
+        <v>97.614314115308147</v>
       </c>
       <c r="D7">
         <v>111</v>
@@ -1486,43 +1509,43 @@
         <v>87.41</v>
       </c>
       <c r="G7">
-        <v>0.6632687113490975</v>
+        <v>0.66326871134909748</v>
       </c>
       <c r="H7">
-        <v>1.207624913284819</v>
+        <v>1.2076249132848189</v>
       </c>
       <c r="I7">
         <v>1.99</v>
       </c>
       <c r="J7">
-        <v>-0.4860847679445895</v>
+        <v>-0.48608476794458949</v>
       </c>
       <c r="K7">
         <v>1.65</v>
       </c>
       <c r="L7">
-        <v>-0.7488266326606212</v>
+        <v>-0.74882663266062122</v>
       </c>
       <c r="M7">
-        <v>85.74400024414062</v>
+        <v>85.744000244140622</v>
       </c>
       <c r="N7">
-        <v>84.78950004577636</v>
+        <v>84.789500045776364</v>
       </c>
       <c r="O7">
-        <v>77.31819992065429</v>
+        <v>77.318199920654294</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>56.95534990310669</v>
+        <v>56.955349903106693</v>
       </c>
       <c r="R7">
         <v>1.01</v>
       </c>
       <c r="S7">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="U7">
         <v>12.22222222222222</v>
@@ -1588,7 +1611,7 @@
         <v>140.63</v>
       </c>
       <c r="AP7">
-        <v>59.56597777272379</v>
+        <v>59.565977772723791</v>
       </c>
     </row>
     <row r="8" spans="1:42">
@@ -1596,10 +1619,10 @@
         <v>48</v>
       </c>
       <c r="B8">
-        <v>98.01192842942345</v>
+        <v>98.011928429423449</v>
       </c>
       <c r="C8">
-        <v>93.83697813121272</v>
+        <v>93.836978131212717</v>
       </c>
       <c r="D8">
         <v>52</v>
@@ -1611,7 +1634,7 @@
         <v>133.82</v>
       </c>
       <c r="G8">
-        <v>0.7377419194776805</v>
+        <v>0.73774191947768053</v>
       </c>
       <c r="H8">
         <v>1.31934915554069</v>
@@ -1620,16 +1643,16 @@
         <v>2.09</v>
       </c>
       <c r="J8">
-        <v>-0.4080744842124751</v>
+        <v>-0.40807448421247511</v>
       </c>
       <c r="K8">
         <v>1.81</v>
       </c>
       <c r="L8">
-        <v>-0.6039931363894547</v>
+        <v>-0.60399313638945473</v>
       </c>
       <c r="M8">
-        <v>130.0339996337891</v>
+        <v>130.03399963378911</v>
       </c>
       <c r="N8">
         <v>125.6110004425049</v>
@@ -1641,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>90.86254989624024</v>
+        <v>90.862549896240239</v>
       </c>
       <c r="R8">
         <v>1.04</v>
@@ -1650,7 +1673,7 @@
         <v>1.05</v>
       </c>
       <c r="U8">
-        <v>2.777777777777778</v>
+        <v>2.7777777777777781</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
@@ -1713,7 +1736,7 @@
         <v>-27.27</v>
       </c>
       <c r="AP8">
-        <v>58.99093966820268</v>
+        <v>58.990939668202678</v>
       </c>
     </row>
     <row r="9" spans="1:42">
@@ -1721,10 +1744,10 @@
         <v>49</v>
       </c>
       <c r="B9">
-        <v>99.80119284294234</v>
+        <v>99.801192842942342</v>
       </c>
       <c r="C9">
-        <v>86.87872763419483</v>
+        <v>86.878727634194831</v>
       </c>
       <c r="D9">
         <v>13</v>
@@ -1736,22 +1759,22 @@
         <v>184.63</v>
       </c>
       <c r="G9">
-        <v>3.004781197078287</v>
+        <v>3.0047811970782869</v>
       </c>
       <c r="H9">
-        <v>2.122045956370504</v>
+        <v>2.1220459563705041</v>
       </c>
       <c r="I9">
         <v>2.73</v>
       </c>
       <c r="J9">
-        <v>0.09119133167305812</v>
+        <v>9.1191331673058124E-2</v>
       </c>
       <c r="K9">
         <v>2.84</v>
       </c>
       <c r="L9">
-        <v>0.3283724958561784</v>
+        <v>0.32837249585617839</v>
       </c>
       <c r="M9">
         <v>180.7399993896484</v>
@@ -1760,13 +1783,13 @@
         <v>180.4529998779297</v>
       </c>
       <c r="O9">
-        <v>171.7609997558594</v>
+        <v>171.76099975585939</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9">
-        <v>129.2984501266479</v>
+        <v>129.29845012664791</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -1838,7 +1861,7 @@
         <v>51.61</v>
       </c>
       <c r="AP9">
-        <v>57.05501524728741</v>
+        <v>57.055015247287407</v>
       </c>
     </row>
     <row r="10" spans="1:42">
@@ -1846,10 +1869,10 @@
         <v>50</v>
       </c>
       <c r="B10">
-        <v>94.83101391650099</v>
+        <v>94.831013916500993</v>
       </c>
       <c r="C10">
-        <v>98.01192842942345</v>
+        <v>98.011928429423449</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1861,7 +1884,7 @@
         <v>252.92</v>
       </c>
       <c r="G10">
-        <v>0.3379809025767415</v>
+        <v>0.33798090257674152</v>
       </c>
       <c r="H10">
         <v>2.021622253860424</v>
@@ -1873,16 +1896,16 @@
         <v>3.149194453971949</v>
       </c>
       <c r="K10">
-        <v>4.52</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="L10">
         <v>1.849124206703425</v>
       </c>
       <c r="M10">
-        <v>239.3459991455078</v>
+        <v>239.34599914550779</v>
       </c>
       <c r="N10">
-        <v>212.8804985046387</v>
+        <v>212.88049850463869</v>
       </c>
       <c r="O10">
         <v>182.3916000366211</v>
@@ -1894,7 +1917,7 @@
         <v>135.9056997680664</v>
       </c>
       <c r="R10">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="S10">
         <v>1.17</v>
@@ -1957,13 +1980,13 @@
         <v>1.67</v>
       </c>
       <c r="AN10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AO10">
         <v>205.39</v>
       </c>
       <c r="AP10">
-        <v>44.53483728221372</v>
+        <v>44.534837282213722</v>
       </c>
     </row>
     <row r="11" spans="1:42">
@@ -1971,10 +1994,10 @@
         <v>51</v>
       </c>
       <c r="B11">
-        <v>97.21669980119285</v>
+        <v>97.216699801192846</v>
       </c>
       <c r="C11">
-        <v>74.75149105367794</v>
+        <v>74.751491053677938</v>
       </c>
       <c r="D11">
         <v>285</v>
@@ -1986,7 +2009,7 @@
         <v>198.51</v>
       </c>
       <c r="G11">
-        <v>0.7162372772030818</v>
+        <v>0.71623727720308183</v>
       </c>
       <c r="H11">
         <v>1.301961763034303</v>
@@ -1995,13 +2018,13 @@
         <v>1.96</v>
       </c>
       <c r="J11">
-        <v>-0.509487853064224</v>
+        <v>-0.50948785306422395</v>
       </c>
       <c r="K11">
         <v>1.62</v>
       </c>
       <c r="L11">
-        <v>-0.7759829132114647</v>
+        <v>-0.77598291321146473</v>
       </c>
       <c r="M11">
         <v>195.9079986572265</v>
@@ -2010,7 +2033,7 @@
         <v>192.3014991760254</v>
       </c>
       <c r="O11">
-        <v>185.4447998046875</v>
+        <v>185.44479980468751</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
@@ -2061,7 +2084,7 @@
         <v>18.82</v>
       </c>
       <c r="AG11">
-        <v>8.970000000000001</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="AH11">
         <v>-3.7</v>
@@ -2088,7 +2111,7 @@
         <v>-6.49</v>
       </c>
       <c r="AP11">
-        <v>43.26386721726777</v>
+        <v>43.263867217267773</v>
       </c>
     </row>
     <row r="12" spans="1:42">
@@ -2096,10 +2119,10 @@
         <v>52</v>
       </c>
       <c r="B12">
-        <v>98.40954274353876</v>
+        <v>98.409542743538765</v>
       </c>
       <c r="C12">
-        <v>99.20477137176938</v>
+        <v>99.204771371769382</v>
       </c>
       <c r="D12">
         <v>49</v>
@@ -2111,7 +2134,7 @@
         <v>151.68</v>
       </c>
       <c r="G12">
-        <v>0.7860161068173189</v>
+        <v>0.78601610681731893</v>
       </c>
       <c r="H12">
         <v>1.878306982969312</v>
@@ -2120,19 +2143,19 @@
         <v>3.44</v>
       </c>
       <c r="J12">
-        <v>0.6450643461710714</v>
+        <v>0.64506434617107145</v>
       </c>
       <c r="K12">
         <v>2.79</v>
       </c>
       <c r="L12">
-        <v>0.2831120282714391</v>
+        <v>0.28311202827143911</v>
       </c>
       <c r="M12">
         <v>145.9119964599609</v>
       </c>
       <c r="N12">
-        <v>141.9664970397949</v>
+        <v>141.96649703979489</v>
       </c>
       <c r="O12">
         <v>123.2183987426758</v>
@@ -2141,16 +2164,16 @@
         <v>1</v>
       </c>
       <c r="Q12">
-        <v>93.45119991302491</v>
+        <v>93.451199913024908</v>
       </c>
       <c r="R12">
         <v>1.03</v>
       </c>
       <c r="S12">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="U12">
-        <v>18.88888888888889</v>
+        <v>18.888888888888889</v>
       </c>
       <c r="V12" t="b">
         <v>0</v>
@@ -2165,7 +2188,7 @@
         <v>56.32</v>
       </c>
       <c r="Z12">
-        <v>153.7</v>
+        <v>153.69999999999999</v>
       </c>
       <c r="AA12">
         <v>190.99</v>
@@ -2174,7 +2197,7 @@
         <v>22.42</v>
       </c>
       <c r="AC12">
-        <v>16.67</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="AD12">
         <v>44.84</v>
@@ -2189,7 +2212,7 @@
         <v>11.83</v>
       </c>
       <c r="AH12">
-        <v>8.140000000000001</v>
+        <v>8.14</v>
       </c>
       <c r="AI12" t="s">
         <v>71</v>
@@ -2207,13 +2230,13 @@
         <v>4.66</v>
       </c>
       <c r="AN12">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="AO12">
-        <v>-8.369999999999999</v>
+        <v>-8.3699999999999992</v>
       </c>
       <c r="AP12">
-        <v>39.42745930845745</v>
+        <v>39.427459308457451</v>
       </c>
     </row>
     <row r="13" spans="1:42">
@@ -2221,10 +2244,10 @@
         <v>53</v>
       </c>
       <c r="B13">
-        <v>93.63817097415506</v>
+        <v>93.638170974155059</v>
       </c>
       <c r="C13">
-        <v>83.1013916500994</v>
+        <v>83.101391650099401</v>
       </c>
       <c r="D13">
         <v>388</v>
@@ -2236,37 +2259,37 @@
         <v>255.12</v>
       </c>
       <c r="G13">
-        <v>0.4613709358440514</v>
+        <v>0.46137093584405142</v>
       </c>
       <c r="H13">
-        <v>0.6581309244840499</v>
+        <v>0.65813092448404986</v>
       </c>
       <c r="I13">
         <v>1.08</v>
       </c>
       <c r="J13">
-        <v>-1.195978349906832</v>
+        <v>-1.1959783499068319</v>
       </c>
       <c r="K13">
         <v>1.54</v>
       </c>
       <c r="L13">
-        <v>-0.8483996613470479</v>
+        <v>-0.84839966134704792</v>
       </c>
       <c r="M13">
-        <v>257.5559997558594</v>
+        <v>257.55599975585938</v>
       </c>
       <c r="N13">
-        <v>257.8404998779297</v>
+        <v>257.84049987792969</v>
       </c>
       <c r="O13">
-        <v>247.7259991455078</v>
+        <v>247.72599914550781</v>
       </c>
       <c r="P13" t="b">
         <v>1</v>
       </c>
       <c r="Q13">
-        <v>225.0124002075195</v>
+        <v>225.01240020751951</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2290,7 +2313,7 @@
         <v>158.65</v>
       </c>
       <c r="Z13">
-        <v>264.79</v>
+        <v>264.79000000000002</v>
       </c>
       <c r="AA13">
         <v>47.06</v>
@@ -2305,7 +2328,7 @@
         <v>95.67</v>
       </c>
       <c r="AE13">
-        <v>-89.29000000000001</v>
+        <v>-89.29</v>
       </c>
       <c r="AF13">
         <v>99.67</v>
@@ -2338,7 +2361,7 @@
         <v>132.41</v>
       </c>
       <c r="AP13">
-        <v>36.69948183226989</v>
+        <v>36.699481832269889</v>
       </c>
     </row>
     <row r="14" spans="1:42">
@@ -2349,7 +2372,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>97.21669980119285</v>
+        <v>97.216699801192846</v>
       </c>
       <c r="D14">
         <v>18</v>
@@ -2361,10 +2384,10 @@
         <v>139.79</v>
       </c>
       <c r="G14">
-        <v>3.811798909016814</v>
+        <v>3.8117989090168138</v>
       </c>
       <c r="H14">
-        <v>2.782863693578815</v>
+        <v>2.7828636935788151</v>
       </c>
       <c r="I14">
         <v>4.66</v>
@@ -2376,13 +2399,13 @@
         <v>3.96</v>
       </c>
       <c r="L14">
-        <v>1.342206969754343</v>
+        <v>1.3422069697543431</v>
       </c>
       <c r="M14">
-        <v>133.7959991455078</v>
+        <v>133.79599914550781</v>
       </c>
       <c r="N14">
-        <v>139.253498840332</v>
+        <v>139.25349884033201</v>
       </c>
       <c r="O14">
         <v>123.6159994506836</v>
@@ -2391,13 +2414,13 @@
         <v>1</v>
       </c>
       <c r="Q14">
-        <v>79.21124969482422</v>
+        <v>79.211249694824218</v>
       </c>
       <c r="R14">
         <v>0.96</v>
       </c>
       <c r="S14">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="U14">
         <v>0</v>
@@ -2415,13 +2438,13 @@
         <v>23</v>
       </c>
       <c r="Z14">
-        <v>153.86</v>
+        <v>153.86000000000001</v>
       </c>
       <c r="AA14">
         <v>119.38</v>
       </c>
       <c r="AB14">
-        <v>-1253.09</v>
+        <v>-1253.0899999999999</v>
       </c>
       <c r="AC14">
         <v>13.38</v>
@@ -2463,7 +2486,7 @@
         <v>-62.94</v>
       </c>
       <c r="AP14">
-        <v>35.57053242779297</v>
+        <v>35.570532427792969</v>
       </c>
     </row>
     <row r="15" spans="1:42">
@@ -2471,10 +2494,10 @@
         <v>55</v>
       </c>
       <c r="B15">
-        <v>92.44532803180915</v>
+        <v>92.445328031809154</v>
       </c>
       <c r="C15">
-        <v>93.04174950298211</v>
+        <v>93.041749502982114</v>
       </c>
       <c r="D15">
         <v>117</v>
@@ -2486,7 +2509,7 @@
         <v>153.82</v>
       </c>
       <c r="G15">
-        <v>0.2889167927120521</v>
+        <v>0.28891679271205212</v>
       </c>
       <c r="H15">
         <v>1.714101711047985</v>
@@ -2495,19 +2518,19 @@
         <v>3.27</v>
       </c>
       <c r="J15">
-        <v>0.5124468638264768</v>
+        <v>0.51244686382647675</v>
       </c>
       <c r="K15">
         <v>3.57</v>
       </c>
       <c r="L15">
-        <v>0.9891753225933748</v>
+        <v>0.98917532259337482</v>
       </c>
       <c r="M15">
-        <v>149.1179992675781</v>
+        <v>149.11799926757811</v>
       </c>
       <c r="N15">
-        <v>147.8555000305176</v>
+        <v>147.85550003051759</v>
       </c>
       <c r="O15">
         <v>143.2413995361328</v>
@@ -2516,7 +2539,7 @@
         <v>1</v>
       </c>
       <c r="Q15">
-        <v>109.48019947052</v>
+        <v>109.48019947052001</v>
       </c>
       <c r="R15">
         <v>1.01</v>
@@ -2585,7 +2608,7 @@
         <v>9.73</v>
       </c>
       <c r="AO15">
-        <v>278.6</v>
+        <v>278.60000000000002</v>
       </c>
       <c r="AP15">
         <v>34.4967791780117</v>
@@ -2596,10 +2619,10 @@
         <v>56</v>
       </c>
       <c r="B16">
-        <v>91.84890656063618</v>
+        <v>91.848906560636181</v>
       </c>
       <c r="C16">
-        <v>70.17892644135189</v>
+        <v>70.178926441351891</v>
       </c>
       <c r="D16">
         <v>283</v>
@@ -2611,28 +2634,28 @@
         <v>783.88</v>
       </c>
       <c r="G16">
-        <v>0.2807767159336748</v>
+        <v>0.28077671593367481</v>
       </c>
       <c r="H16">
-        <v>1.447651723082022</v>
+        <v>1.4476517230820221</v>
       </c>
       <c r="I16">
         <v>1.71</v>
       </c>
       <c r="J16">
-        <v>-0.7045135623945102</v>
+        <v>-0.70451356239451024</v>
       </c>
       <c r="K16">
         <v>1.5</v>
       </c>
       <c r="L16">
-        <v>-0.8846080354148396</v>
+        <v>-0.88460803541483957</v>
       </c>
       <c r="M16">
         <v>760.3119995117188</v>
       </c>
       <c r="N16">
-        <v>774.9245056152344</v>
+        <v>774.92450561523435</v>
       </c>
       <c r="O16">
         <v>767.2002014160156</v>
@@ -2641,7 +2664,7 @@
         <v>1</v>
       </c>
       <c r="Q16">
-        <v>655.1733003234863</v>
+        <v>655.17330032348627</v>
       </c>
       <c r="R16">
         <v>0.98</v>
@@ -2650,7 +2673,7 @@
         <v>1.01</v>
       </c>
       <c r="U16">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="V16" t="b">
         <v>0</v>
@@ -2713,7 +2736,7 @@
         <v>-19.18</v>
       </c>
       <c r="AP16">
-        <v>34.40101771720058</v>
+        <v>34.401017717200581</v>
       </c>
     </row>
     <row r="17" spans="1:42">
@@ -2721,10 +2744,10 @@
         <v>57</v>
       </c>
       <c r="B17">
-        <v>92.6441351888668</v>
+        <v>92.644135188866798</v>
       </c>
       <c r="C17">
-        <v>61.23260437375746</v>
+        <v>61.232604373757461</v>
       </c>
       <c r="D17">
         <v>54</v>
@@ -2736,7 +2759,7 @@
         <v>98.78</v>
       </c>
       <c r="G17">
-        <v>0.3501485311217564</v>
+        <v>0.35014853112175642</v>
       </c>
       <c r="H17">
         <v>1.309542948445604</v>
@@ -2745,28 +2768,28 @@
         <v>1.87</v>
       </c>
       <c r="J17">
-        <v>-0.5796971084231269</v>
+        <v>-0.57969710842312694</v>
       </c>
       <c r="K17">
         <v>1.49</v>
       </c>
       <c r="L17">
-        <v>-0.8936601289317875</v>
+        <v>-0.89366012893178748</v>
       </c>
       <c r="M17">
-        <v>97.86400146484375</v>
+        <v>97.864001464843753</v>
       </c>
       <c r="N17">
-        <v>97.96100006103515</v>
+        <v>97.961000061035151</v>
       </c>
       <c r="O17">
-        <v>97.8950001525879</v>
+        <v>97.895000152587897</v>
       </c>
       <c r="P17" t="b">
         <v>1</v>
       </c>
       <c r="Q17">
-        <v>82.98415006637573</v>
+        <v>82.984150066375733</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -2775,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="U17">
-        <v>2.222222222222222</v>
+        <v>2.2222222222222219</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
@@ -2838,7 +2861,7 @@
         <v>0.98</v>
       </c>
       <c r="AP17">
-        <v>34.10054158127485</v>
+        <v>34.100541581274847</v>
       </c>
     </row>
     <row r="18" spans="1:42">
@@ -2846,10 +2869,10 @@
         <v>58</v>
       </c>
       <c r="B18">
-        <v>96.42147117296223</v>
+        <v>96.421471172962228</v>
       </c>
       <c r="C18">
-        <v>78.52882703777337</v>
+        <v>78.528827037773368</v>
       </c>
       <c r="D18">
         <v>142</v>
@@ -2861,37 +2884,37 @@
         <v>303.87</v>
       </c>
       <c r="G18">
-        <v>0.4818979509696636</v>
+        <v>0.48189795096966359</v>
       </c>
       <c r="H18">
-        <v>1.134725368717625</v>
+        <v>1.1347253687176251</v>
       </c>
       <c r="I18">
         <v>1.46</v>
       </c>
       <c r="J18">
-        <v>-0.8995392717247966</v>
+        <v>-0.89953927172479664</v>
       </c>
       <c r="K18">
         <v>1.41</v>
       </c>
       <c r="L18">
-        <v>-0.9660768770673707</v>
+        <v>-0.96607687706737067</v>
       </c>
       <c r="M18">
-        <v>303.4920043945312</v>
+        <v>303.49200439453119</v>
       </c>
       <c r="N18">
-        <v>300.0155014038086</v>
+        <v>300.01550140380863</v>
       </c>
       <c r="O18">
-        <v>288.9536004638672</v>
+        <v>288.95360046386719</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
       </c>
       <c r="Q18">
-        <v>238.1190501403809</v>
+        <v>238.11905014038089</v>
       </c>
       <c r="R18">
         <v>1.01</v>
@@ -2912,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="Y18">
-        <v>159.36</v>
+        <v>159.36000000000001</v>
       </c>
       <c r="Z18">
-        <v>316.53</v>
+        <v>316.52999999999997</v>
       </c>
       <c r="AA18">
         <v>323.18</v>
@@ -2927,7 +2950,7 @@
         <v>31.81</v>
       </c>
       <c r="AD18">
-        <v>19.92</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="AE18">
         <v>42.74</v>
@@ -2936,7 +2959,7 @@
         <v>3.24</v>
       </c>
       <c r="AG18">
-        <v>5.11</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="AH18">
         <v>2.92</v>
@@ -2963,7 +2986,7 @@
         <v>-29.95</v>
       </c>
       <c r="AP18">
-        <v>34.00456889858429</v>
+        <v>34.004568898584289</v>
       </c>
     </row>
     <row r="19" spans="1:42">
@@ -2971,10 +2994,10 @@
         <v>59</v>
       </c>
       <c r="B19">
-        <v>97.01789264413519</v>
+        <v>97.017892644135188</v>
       </c>
       <c r="C19">
-        <v>60.03976143141153</v>
+        <v>60.039761431411527</v>
       </c>
       <c r="D19">
         <v>127</v>
@@ -2986,37 +3009,37 @@
         <v>68.75</v>
       </c>
       <c r="G19">
-        <v>0.5980340852382821</v>
+        <v>0.59803408523828205</v>
       </c>
       <c r="H19">
-        <v>1.675814563963257</v>
+        <v>1.6758145639632569</v>
       </c>
       <c r="I19">
         <v>2.48</v>
       </c>
       <c r="J19">
-        <v>-0.1038343776572282</v>
+        <v>-0.10383437765722819</v>
       </c>
       <c r="K19">
         <v>2.21</v>
       </c>
       <c r="L19">
-        <v>-0.2419093957115389</v>
+        <v>-0.24190939571153891</v>
       </c>
       <c r="M19">
-        <v>66.77999877929688</v>
+        <v>66.779998779296875</v>
       </c>
       <c r="N19">
-        <v>68.9319995880127</v>
+        <v>68.931999588012701</v>
       </c>
       <c r="O19">
-        <v>65.51279983520507</v>
+        <v>65.512799835205072</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
       </c>
       <c r="Q19">
-        <v>54.9756248664856</v>
+        <v>54.975624866485603</v>
       </c>
       <c r="R19">
         <v>0.97</v>
@@ -3040,7 +3063,7 @@
         <v>32.82</v>
       </c>
       <c r="Z19">
-        <v>73.34999999999999</v>
+        <v>73.349999999999994</v>
       </c>
       <c r="AA19">
         <v>114.18</v>
@@ -3049,10 +3072,10 @@
         <v>27.01</v>
       </c>
       <c r="AC19">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="AD19">
-        <v>40.48</v>
+        <v>40.479999999999997</v>
       </c>
       <c r="AE19">
         <v>19.82</v>
@@ -3088,7 +3111,7 @@
         <v>232.21</v>
       </c>
       <c r="AP19">
-        <v>33.24221835345165</v>
+        <v>33.242218353451648</v>
       </c>
     </row>
     <row r="20" spans="1:42">
@@ -3096,10 +3119,10 @@
         <v>60</v>
       </c>
       <c r="B20">
-        <v>95.42743538767395</v>
+        <v>95.427435387673953</v>
       </c>
       <c r="C20">
-        <v>78.72763419483101</v>
+        <v>78.727634194831012</v>
       </c>
       <c r="D20">
         <v>478</v>
@@ -3111,7 +3134,7 @@
         <v>335.67</v>
       </c>
       <c r="G20">
-        <v>0.4682631297590104</v>
+        <v>0.46826312975901041</v>
       </c>
       <c r="H20">
         <v>1.483329561838187</v>
@@ -3120,28 +3143,28 @@
         <v>1.53</v>
       </c>
       <c r="J20">
-        <v>-0.8449320731123164</v>
+        <v>-0.84493207311231644</v>
       </c>
       <c r="K20">
         <v>1.95</v>
       </c>
       <c r="L20">
-        <v>-0.4772638271521842</v>
+        <v>-0.47726382715218418</v>
       </c>
       <c r="M20">
-        <v>334.4120056152344</v>
+        <v>334.41200561523442</v>
       </c>
       <c r="N20">
-        <v>323.3815048217774</v>
+        <v>323.38150482177741</v>
       </c>
       <c r="O20">
-        <v>311.7736022949219</v>
+        <v>311.77360229492189</v>
       </c>
       <c r="P20" t="b">
         <v>1</v>
       </c>
       <c r="Q20">
-        <v>270.8856507873535</v>
+        <v>270.88565078735348</v>
       </c>
       <c r="R20">
         <v>1.03</v>
@@ -3177,10 +3200,10 @@
         <v>20.96</v>
       </c>
       <c r="AD20">
-        <v>35.12</v>
+        <v>35.119999999999997</v>
       </c>
       <c r="AE20">
-        <v>32.55</v>
+        <v>32.549999999999997</v>
       </c>
       <c r="AF20">
         <v>74.88</v>
@@ -3213,7 +3236,7 @@
         <v>4.24</v>
       </c>
       <c r="AP20">
-        <v>32.81176375822719</v>
+        <v>32.811763758227187</v>
       </c>
     </row>
     <row r="21" spans="1:42">
@@ -3236,7 +3259,7 @@
         <v>212.44</v>
       </c>
       <c r="G21">
-        <v>0.5000602585019227</v>
+        <v>0.50006025850192271</v>
       </c>
       <c r="H21">
         <v>1.398827614008249</v>
@@ -3245,28 +3268,28 @@
         <v>2.61</v>
       </c>
       <c r="J21">
-        <v>-0.002421008805479413</v>
+        <v>-2.4210088054794129E-3</v>
       </c>
       <c r="K21">
         <v>2.39</v>
       </c>
       <c r="L21">
-        <v>-0.07897171240647666</v>
+        <v>-7.8971712406476657E-2</v>
       </c>
       <c r="M21">
-        <v>204.5800018310547</v>
+        <v>204.58000183105469</v>
       </c>
       <c r="N21">
-        <v>206.1845001220703</v>
+        <v>206.18450012207029</v>
       </c>
       <c r="O21">
-        <v>210.2999993896484</v>
+        <v>210.29999938964841</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>181.5395994186401</v>
+        <v>181.53959941864011</v>
       </c>
       <c r="R21">
         <v>0.99</v>
@@ -3302,7 +3325,7 @@
         <v>13.4</v>
       </c>
       <c r="AD21">
-        <v>68.81999999999999</v>
+        <v>68.819999999999993</v>
       </c>
       <c r="AE21">
         <v>40.43</v>
@@ -3335,10 +3358,10 @@
         <v>10.01</v>
       </c>
       <c r="AO21">
-        <v>64.09999999999999</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="AP21">
-        <v>32.24928599336694</v>
+        <v>32.249285993366939</v>
       </c>
     </row>
     <row r="22" spans="1:42">
@@ -3346,7 +3369,7 @@
         <v>62</v>
       </c>
       <c r="B22">
-        <v>92.04771371769384</v>
+        <v>92.047713717693838</v>
       </c>
       <c r="C22">
         <v>62.42544731610338</v>
@@ -3361,37 +3384,37 @@
         <v>97.2</v>
       </c>
       <c r="G22">
-        <v>0.4221967554747781</v>
+        <v>0.42219675547477808</v>
       </c>
       <c r="H22">
-        <v>0.5259628906903532</v>
+        <v>0.52596289069035318</v>
       </c>
       <c r="I22">
         <v>1.87</v>
       </c>
       <c r="J22">
-        <v>-0.5796971084231269</v>
+        <v>-0.57969710842312694</v>
       </c>
       <c r="K22">
         <v>1.71</v>
       </c>
       <c r="L22">
-        <v>-0.6945140715589337</v>
+        <v>-0.69451407155893374</v>
       </c>
       <c r="M22">
-        <v>95.74400024414062</v>
+        <v>95.744000244140622</v>
       </c>
       <c r="N22">
-        <v>91.95200004577637</v>
+        <v>91.952000045776373</v>
       </c>
       <c r="O22">
-        <v>92.82139999389648</v>
+        <v>92.821399993896478</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>77.30034996032715</v>
+        <v>77.300349960327154</v>
       </c>
       <c r="R22">
         <v>1.04</v>
@@ -3463,7 +3486,7 @@
         <v>13.97</v>
       </c>
       <c r="AP22">
-        <v>31.51079685876338</v>
+        <v>31.510796858763381</v>
       </c>
     </row>
     <row r="23" spans="1:42">
@@ -3471,10 +3494,10 @@
         <v>63</v>
       </c>
       <c r="B23">
-        <v>93.04174950298211</v>
+        <v>93.041749502982114</v>
       </c>
       <c r="C23">
-        <v>96.81908548707754</v>
+        <v>96.819085487077544</v>
       </c>
       <c r="D23">
         <v>30</v>
@@ -3486,7 +3509,7 @@
         <v>260.51</v>
       </c>
       <c r="G23">
-        <v>0.4034902628439309</v>
+        <v>0.40349026284393091</v>
       </c>
       <c r="H23">
         <v>1.06252669067432</v>
@@ -3495,28 +3518,28 @@
         <v>1.51</v>
       </c>
       <c r="J23">
-        <v>-0.8605341298587393</v>
+        <v>-0.86053412985873934</v>
       </c>
       <c r="K23">
         <v>1.76</v>
       </c>
       <c r="L23">
-        <v>-0.6492536039741942</v>
+        <v>-0.64925360397419418</v>
       </c>
       <c r="M23">
         <v>255.0259979248047</v>
       </c>
       <c r="N23">
-        <v>248.6735000610352</v>
+        <v>248.67350006103521</v>
       </c>
       <c r="O23">
-        <v>237.1610006713867</v>
+        <v>237.16100067138669</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
       </c>
       <c r="Q23">
-        <v>191.9633501434326</v>
+        <v>191.96335014343259</v>
       </c>
       <c r="R23">
         <v>1.03</v>
@@ -3579,16 +3602,16 @@
         <v>110</v>
       </c>
       <c r="AM23">
-        <v>9.640000000000001</v>
+        <v>9.64</v>
       </c>
       <c r="AN23">
-        <v>8.949999999999999</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="AO23">
         <v>-7.16</v>
       </c>
       <c r="AP23">
-        <v>30.65119119867886</v>
+        <v>30.651191198678859</v>
       </c>
     </row>
     <row r="24" spans="1:42">
@@ -3596,10 +3619,10 @@
         <v>64</v>
       </c>
       <c r="B24">
-        <v>93.24055666003976</v>
+        <v>93.240556660039758</v>
       </c>
       <c r="C24">
-        <v>97.01789264413519</v>
+        <v>97.017892644135188</v>
       </c>
       <c r="D24">
         <v>16</v>
@@ -3620,19 +3643,19 @@
         <v>1.55</v>
       </c>
       <c r="J24">
-        <v>-0.8293300163658935</v>
+        <v>-0.82933001636589354</v>
       </c>
       <c r="K24">
         <v>1.79</v>
       </c>
       <c r="L24">
-        <v>-0.6220973234233506</v>
+        <v>-0.62209732342335056</v>
       </c>
       <c r="M24">
-        <v>254.3400024414063</v>
+        <v>254.34000244140631</v>
       </c>
       <c r="N24">
-        <v>247.954500579834</v>
+        <v>247.95450057983399</v>
       </c>
       <c r="O24">
         <v>236.538200378418</v>
@@ -3641,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="Q24">
-        <v>190.6712001037598</v>
+        <v>190.67120010375979</v>
       </c>
       <c r="R24">
         <v>1.03</v>
@@ -3704,10 +3727,10 @@
         <v>110</v>
       </c>
       <c r="AM24">
-        <v>9.640000000000001</v>
+        <v>9.64</v>
       </c>
       <c r="AN24">
-        <v>8.960000000000001</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="AO24">
         <v>-7.05</v>
@@ -3721,7 +3744,7 @@
         <v>65</v>
       </c>
       <c r="B25">
-        <v>95.02982107355865</v>
+        <v>95.029821073558651</v>
       </c>
       <c r="C25">
         <v>89.26441351888667</v>
@@ -3736,7 +3759,7 @@
         <v>748.24</v>
       </c>
       <c r="G25">
-        <v>0.4588970823751021</v>
+        <v>0.45889708237510213</v>
       </c>
       <c r="H25">
         <v>1.344161123380011</v>
@@ -3745,28 +3768,28 @@
         <v>2.61</v>
       </c>
       <c r="J25">
-        <v>-0.002421008805479413</v>
+        <v>-2.4210088054794129E-3</v>
       </c>
       <c r="K25">
         <v>1.96</v>
       </c>
       <c r="L25">
-        <v>-0.4682117336352363</v>
+        <v>-0.46821173363523633</v>
       </c>
       <c r="M25">
         <v>699.5160034179687</v>
       </c>
       <c r="N25">
-        <v>677.9035034179688</v>
+        <v>677.90350341796875</v>
       </c>
       <c r="O25">
-        <v>645.9000024414063</v>
+        <v>645.90000244140629</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
       </c>
       <c r="Q25">
-        <v>512.5981504821777</v>
+        <v>512.59815048217774</v>
       </c>
       <c r="R25">
         <v>1.03</v>
@@ -3846,7 +3869,7 @@
         <v>66</v>
       </c>
       <c r="B26">
-        <v>92.2465208747515</v>
+        <v>92.246520874751496</v>
       </c>
       <c r="C26">
         <v>82.7037773359841</v>
@@ -3861,37 +3884,37 @@
         <v>250.45</v>
       </c>
       <c r="G26">
-        <v>0.3541261077433148</v>
+        <v>0.35412610774331482</v>
       </c>
       <c r="H26">
-        <v>1.172279268613374</v>
+        <v>1.1722792686133741</v>
       </c>
       <c r="I26">
         <v>1.47</v>
       </c>
       <c r="J26">
-        <v>-0.8917382433515851</v>
+        <v>-0.89173824335158514</v>
       </c>
       <c r="K26">
         <v>1.36</v>
       </c>
       <c r="L26">
-        <v>-1.01133734465211</v>
+        <v>-1.0113373446521099</v>
       </c>
       <c r="M26">
         <v>249.7279998779297</v>
       </c>
       <c r="N26">
-        <v>251.7229995727539</v>
+        <v>251.72299957275391</v>
       </c>
       <c r="O26">
-        <v>242.3629995727539</v>
+        <v>242.36299957275389</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
       </c>
       <c r="Q26">
-        <v>218.7668001556397</v>
+        <v>218.76680015563969</v>
       </c>
       <c r="R26">
         <v>0.99</v>
@@ -3912,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>160.95</v>
+        <v>160.94999999999999</v>
       </c>
       <c r="Z26">
         <v>261.69</v>
@@ -3963,7 +3986,7 @@
         <v>-7.79</v>
       </c>
       <c r="AP26">
-        <v>23.07073949623602</v>
+        <v>23.070739496236019</v>
       </c>
     </row>
     <row r="27" spans="1:42">
@@ -3971,10 +3994,10 @@
         <v>67</v>
       </c>
       <c r="B27">
-        <v>93.83697813121272</v>
+        <v>93.836978131212717</v>
       </c>
       <c r="C27">
-        <v>82.90258449304176</v>
+        <v>82.902584493041758</v>
       </c>
       <c r="D27">
         <v>271</v>
@@ -3986,10 +4009,10 @@
         <v>235.65</v>
       </c>
       <c r="G27">
-        <v>0.4234508873437269</v>
+        <v>0.42345088734372688</v>
       </c>
       <c r="H27">
-        <v>1.176453379853568</v>
+        <v>1.1764533798535679</v>
       </c>
       <c r="I27">
         <v>1.23</v>
@@ -3998,7 +4021,7 @@
         <v>-1.07896292430866</v>
       </c>
       <c r="K27">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="L27">
         <v>-1.22858758905886</v>
@@ -4007,10 +4030,10 @@
         <v>230.6040008544922</v>
       </c>
       <c r="N27">
-        <v>223.5175010681152</v>
+        <v>223.51750106811519</v>
       </c>
       <c r="O27">
-        <v>215.0880001831055</v>
+        <v>215.08800018310549</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -4025,7 +4048,7 @@
         <v>1.04</v>
       </c>
       <c r="U27">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="V27" t="b">
         <v>0</v>
@@ -4061,7 +4084,7 @@
         <v>5300</v>
       </c>
       <c r="AG27">
-        <v>-97.73999999999999</v>
+        <v>-97.74</v>
       </c>
       <c r="AH27">
         <v>82.47</v>
@@ -4079,7 +4102,7 @@
         <v>112</v>
       </c>
       <c r="AM27">
-        <v>4.85</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="AN27">
         <v>8.99</v>
@@ -4096,10 +4119,10 @@
         <v>68</v>
       </c>
       <c r="B28">
-        <v>96.62027833001989</v>
+        <v>96.620278330019886</v>
       </c>
       <c r="C28">
-        <v>96.62027833001989</v>
+        <v>96.620278330019886</v>
       </c>
       <c r="D28">
         <v>409</v>
@@ -4111,22 +4134,22 @@
         <v>1182.82</v>
       </c>
       <c r="G28">
-        <v>0.511662259214731</v>
+        <v>0.51166225921473096</v>
       </c>
       <c r="H28">
-        <v>1.681985171672057</v>
+        <v>1.6819851716720571</v>
       </c>
       <c r="I28">
         <v>3.37</v>
       </c>
       <c r="J28">
-        <v>0.5904571475585914</v>
+        <v>0.59045714755859136</v>
       </c>
       <c r="K28">
         <v>2.68</v>
       </c>
       <c r="L28">
-        <v>0.1835389995850124</v>
+        <v>0.18353899958501241</v>
       </c>
       <c r="M28">
         <v>1151.2919921875</v>
@@ -4141,13 +4164,13 @@
         <v>1</v>
       </c>
       <c r="Q28">
-        <v>833.4499490356445</v>
+        <v>833.44994903564452</v>
       </c>
       <c r="R28">
         <v>1.05</v>
       </c>
       <c r="S28">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="U28">
         <v>1.666666666666667</v>
@@ -4162,7 +4185,7 @@
         <v>1</v>
       </c>
       <c r="Y28">
-        <v>551.33</v>
+        <v>551.33000000000004</v>
       </c>
       <c r="Z28">
         <v>1191.26</v>
@@ -4213,7 +4236,7 @@
         <v>5.91</v>
       </c>
       <c r="AP28">
-        <v>19.44633890082216</v>
+        <v>19.446338900822159</v>
       </c>
     </row>
     <row r="29" spans="1:42">
@@ -4221,10 +4244,10 @@
         <v>69</v>
       </c>
       <c r="B29">
-        <v>90.65606361829026</v>
+        <v>90.656063618290261</v>
       </c>
       <c r="C29">
-        <v>57.25646123260437</v>
+        <v>57.256461232604373</v>
       </c>
       <c r="D29">
         <v>313</v>
@@ -4233,40 +4256,40 @@
         <v>272</v>
       </c>
       <c r="F29">
-        <v>161.89</v>
+        <v>161.88999999999999</v>
       </c>
       <c r="G29">
-        <v>0.3545605244675659</v>
+        <v>0.35456052446756592</v>
       </c>
       <c r="H29">
-        <v>0.4375842992185823</v>
+        <v>0.43758429921858227</v>
       </c>
       <c r="I29">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="J29">
-        <v>-1.149172179667563</v>
+        <v>-1.1491721796675629</v>
       </c>
       <c r="K29">
         <v>1.72</v>
       </c>
       <c r="L29">
-        <v>-0.6854619780419858</v>
+        <v>-0.68546197804198583</v>
       </c>
       <c r="M29">
-        <v>159.3040008544922</v>
+        <v>159.30400085449219</v>
       </c>
       <c r="N29">
         <v>156.8225021362305</v>
       </c>
       <c r="O29">
-        <v>152.7804010009766</v>
+        <v>152.78040100097661</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
       </c>
       <c r="Q29">
-        <v>145.41225025177</v>
+        <v>145.41225025176999</v>
       </c>
       <c r="R29">
         <v>1.02</v>
@@ -4326,13 +4349,13 @@
         <v>6.56</v>
       </c>
       <c r="AN29">
-        <v>8.640000000000001</v>
+        <v>8.64</v>
       </c>
       <c r="AO29">
         <v>31.71</v>
       </c>
       <c r="AP29">
-        <v>11.45473950295746</v>
+        <v>11.454739502957461</v>
       </c>
     </row>
     <row r="30" spans="1:42">
@@ -4340,10 +4363,10 @@
         <v>70</v>
       </c>
       <c r="B30">
-        <v>91.05367793240556</v>
+        <v>91.053677932405563</v>
       </c>
       <c r="C30">
-        <v>77.93240556660039</v>
+        <v>77.932405566600394</v>
       </c>
       <c r="D30">
         <v>213</v>
@@ -4355,43 +4378,43 @@
         <v>389.19</v>
       </c>
       <c r="G30">
-        <v>0.1918138099312534</v>
+        <v>0.19181380993125341</v>
       </c>
       <c r="H30">
-        <v>1.703377545035803</v>
+        <v>1.7033775450358031</v>
       </c>
       <c r="I30">
         <v>3.35</v>
       </c>
       <c r="J30">
-        <v>0.5748550908121685</v>
+        <v>0.57485509081216846</v>
       </c>
       <c r="K30">
         <v>2.66</v>
       </c>
       <c r="L30">
-        <v>0.1654348125511166</v>
+        <v>0.16543481255111661</v>
       </c>
       <c r="M30">
-        <v>366.7679992675781</v>
+        <v>366.76799926757809</v>
       </c>
       <c r="N30">
-        <v>368.3982513427734</v>
+        <v>368.39825134277339</v>
       </c>
       <c r="O30">
-        <v>338.6790997314453</v>
+        <v>338.67909973144532</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
       </c>
       <c r="Q30">
-        <v>294.1677248382568</v>
+        <v>294.16772483825679</v>
       </c>
       <c r="R30">
         <v>1</v>
       </c>
       <c r="S30">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="U30">
         <v>0</v>
@@ -4451,16 +4474,17 @@
         <v>9.57</v>
       </c>
       <c r="AN30">
-        <v>8.949999999999999</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="AO30">
         <v>-6.48</v>
       </c>
       <c r="AP30">
-        <v>5.827692188078467</v>
+        <v>5.8276921880784673</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>